--- a/BAU_Lahan.xlsx
+++ b/BAU_Lahan.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{A89E85FA-3A8D-4825-ABE8-254E23969C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A7F2A6-0253-459D-AC4B-580A75A2BB83}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{506DD584-05C3-4D62-9210-8A003C1A68C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{506DD584-05C3-4D62-9210-8A003C1A68C8}"/>
   </bookViews>
   <sheets>
     <sheet name="BAU_Lahan" sheetId="1" r:id="rId1"/>
